--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/region-aysen-del-general-carlos-ibanez-del-campo.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/region-aysen-del-general-carlos-ibanez-del-campo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>749-20-CM26</t>
+          <t>4140-5-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>829.37</v>
+        <v>1206.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>886182-219-CM26</t>
+          <t>707426-7-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL TREBOL LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.601.801-5</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1004.69</v>
+        <v>682.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>951405-286-CM26</t>
+          <t>3791-104-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL Y DISTRIBUIDORA ULAP LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.173.807-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14421.18</v>
+        <v>6028.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2713-876-CM26</t>
+          <t>3791-155-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>942.88</v>
+        <v>788.0700000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>951405-306-CM26</t>
+          <t>3797-85-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1425.14</v>
+        <v>4624.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2713-936-CM26</t>
+          <t>1005-16-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1330.79</v>
+        <v>2209.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2713-937-CM26</t>
+          <t>742-16-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,6 +935,3666 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>937.6900000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1195-77-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>19096.22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3797-116-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.254.500-1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>831.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>749-9-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>726.79</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>854-39-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>3031.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>854-38-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>3031.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>907-50-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>14015.49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1403-3147-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>2180.07</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3791-329-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1210.17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>930039-17-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>2207.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>951405-119-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>2564.31</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2713-354-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>6126.33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1286987-39-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>65.797.310-6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>909.13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2713-416-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>15233.96</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1057062-130-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>4437.34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2713-429-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>12549.74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2713-434-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>12855.62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1195-242-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>35995.21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3431-92-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>1059.18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3431-97-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3431-101-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>4025.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1043-68-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>21370.19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1403-3869-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>2234.48</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>854-215-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>4648.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>707426-118-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>FUEGOCLIMA SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.190.725-3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>5332.46</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5019-2085-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>65.224.300-2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>RUBCES</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>77.266.920-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>14176.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2182-99-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1211.51</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>854-234-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>2467.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>854-235-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>2467.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2713-598-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>3139.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2713-599-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>3285.39</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2713-583-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>781.9299999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2713-613-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>1781.52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1286987-69-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>65.797.310-6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1045.07</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2151-244-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1211.16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4609-300-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>HQT</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.399.126-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>4274.36</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>5019-2105-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>65.224.300-2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>RUBCES</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.266.920-8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1404.9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4649-133-CM25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>30351.61</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4649-134-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>10561.12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1079689-237-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>902.61</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>930039-43-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>1276.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3431-123-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>FUEGOCLIMA SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.190.725-3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1116.19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1079689-261-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>13119.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1113146-45-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>1977.16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>749-44-CM25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>746.73</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1195-465-CM25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>10359.62</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2713-929-CM25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>21769.32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>951405-326-CM25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>7218.56</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>854-326-CM25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>2227.31</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>854-327-CM25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>2227.31</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1005-123-CM25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1424.07</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4609-487-CM25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>HQT</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.399.126-1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>4483.36</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3797-708-CM25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.254.500-1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>11285.25</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1079689-348-CM25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>3108.19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>749-20-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>829.37</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>886182-219-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COMERCIAL TREBOL LIMITADA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>77.601.801-5</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1004.69</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>951405-286-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>14421.18</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2713-876-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>942.88</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2713-936-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>1330.79</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>951405-306-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>1425.14</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2713-937-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
         <v>813.89</v>
       </c>
     </row>
